--- a/AMZN_Recruitment_Pipeline_Tracker.xlsx
+++ b/AMZN_Recruitment_Pipeline_Tracker.xlsx
@@ -1,22 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/312B8570E4D1FE3F/Documents/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="172" documentId="8_{96090942-BB65-4B43-AC4D-A906946F7D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B1C30DA-2358-487B-845F-D929F4D93C55}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Master Pipeline" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Metrics Dashboard" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Search Console" sheetId="3" r:id="rId7"/>
+    <sheet name="Master Pipeline" sheetId="1" r:id="rId1"/>
+    <sheet name="Metrics Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="Search Console" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="4" r:id="rId4"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>Candidate_ID</t>
   </si>
@@ -78,9 +98,6 @@
     <t>Sourced</t>
   </si>
   <si>
-    <t>COUNTA of Candidate_ID</t>
-  </si>
-  <si>
     <t>Grand Total</t>
   </si>
   <si>
@@ -94,22 +111,76 @@
   </si>
   <si>
     <t>Current Stage:</t>
+  </si>
+  <si>
+    <t>Total Candidates</t>
+  </si>
+  <si>
+    <t>Interview Stage</t>
+  </si>
+  <si>
+    <t>Candidate Profile Lookup Tool</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -118,123 +189,1419 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[AMZN_Recruitment_Pipeline_Tracker.xlsx]Metrics Dashboard!Metrics Dashboard</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Active</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Candidates by Stage</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.26074534161490681"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1"/>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="84000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="1"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Metrics Dashboard'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="84000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="1"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="20000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Metrics Dashboard'!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Assessment Loop</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Initial Screening</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sourced</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Metrics Dashboard'!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9C74-495D-9AD2-7FB58A60253A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="41"/>
+        <c:axId val="1027766015"/>
+        <c:axId val="1027770815"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1027766015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1027770815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1027770815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1027766015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="68000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="5400000" scaled="1"/>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="204">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200">
+      <a:effectLst/>
+    </cs:defRPr>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="68000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr/>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="84000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="84000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="84000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="84000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="1"/>
+      </a:gradFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="76200" dir="18900000" sy="23000" kx="-1200000" algn="bl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr kern="1200">
+      <a:effectLst/>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>320040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C91147B3-0F43-A2D2-1BEA-A97BAD98F653}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" invalid="1" refreshOnLoad="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="user" refreshedDate="46186.877973958333" refreshedVersion="8" recordCount="5" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D6" sheet="Master Pipeline"/>
   </cacheSource>
-  <cacheFields>
+  <cacheFields count="4">
     <cacheField name="Candidate_ID" numFmtId="0">
-      <sharedItems>
-        <s v="AMZN-001"/>
-        <s v="AMZN-002"/>
-        <s v="AMZN-003"/>
-        <s v="AMZN-004"/>
-        <s v="AMZN-005"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Full_Name" numFmtId="0">
-      <sharedItems>
-        <s v="Aarav Sharma"/>
-        <s v="Priya Patel"/>
-        <s v="Rohan Das"/>
-        <s v="Ananya Reddy"/>
-        <s v="Vikram Malhotra"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Target_Role" numFmtId="0">
-      <sharedItems>
-        <s v="Cloud Support Associate"/>
-        <s v="Operations Manager"/>
-        <s v="HR Operations Specialist"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Interview_Stage" numFmtId="0">
-      <sharedItems>
+      <sharedItems count="3">
         <s v="Assessment Loop"/>
         <s v="Initial Screening"/>
         <s v="Sourced"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <s v="AMZN-001"/>
+    <s v="Aarav Sharma"/>
+    <s v="Cloud Support Associate"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="AMZN-002"/>
+    <s v="Priya Patel"/>
+    <s v="Operations Manager"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="AMZN-003"/>
+    <s v="Rohan Das"/>
+    <s v="Cloud Support Associate"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="AMZN-004"/>
+    <s v="Ananya Reddy"/>
+    <s v="HR Operations Specialist"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="AMZN-005"/>
+    <s v="Vikram Malhotra"/>
+    <s v="Operations Manager"/>
+    <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Metrics Dashboard" cacheId="0" dataCaption="" compact="0" compactData="0">
-  <location ref="A1:B5" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields>
-    <pivotField name="Candidate_ID" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="Full_Name" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="Target_Role" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField name="Interview_Stage" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="Metrics Dashboard" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="8" compact="0" compactData="0" chartFormat="3">
+  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField name="Candidate_ID" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="Full_Name" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="Target_Role" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="Interview Stage" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items count="4">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -242,17 +1609,97 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields>
+  <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <dataFields>
-    <dataField name="COUNTA of Candidate_ID" fld="0" subtotal="count" baseField="0"/>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Candidates" fld="0" subtotal="count" baseField="0"/>
   </dataFields>
+  <formats count="12">
+    <format dxfId="23">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium21" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -442,45 +1889,54 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -494,7 +1950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -508,7 +1964,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -522,7 +1978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -537,75 +1993,130 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D6">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Sourced,Initial Screening,Assessment Loop,Background Check,Offer Extended"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="11">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.109375" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" ht="25.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="10"/>
+    </row>
+    <row r="2" spans="1:2" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="22.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
+      <c r="B3" s="6" t="str">
+        <f>VLOOKUP(B2,'Master Pipeline'!A:E,2, FALSE)</f>
+        <v>Priya Patel</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="str">
-        <f t="array" ref="B3">XLOOKUP(B1, 'Master Pipeline'!A:A, 'Master Pipeline'!B:B, "ID Not Found")</f>
-        <v>Aarav Sharma</v>
+      <c r="B4" s="6" t="str">
+        <f>VLOOKUP(B2,'Master Pipeline'!A:E,3,FALSE)</f>
+        <v>Operations Manager</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="str">
-        <f t="array" ref="B4">XLOOKUP(B1, 'Master Pipeline'!A:A, 'Master Pipeline'!C:C, "")</f>
-        <v>Cloud Support Associate</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <f t="array" ref="B5">XLOOKUP(B1, 'Master Pipeline'!A:A, 'Master Pipeline'!D:D, "")</f>
-        <v>Assessment Loop</v>
+      <c r="B5" s="6" t="str">
+        <f>VLOOKUP(B2,'Master Pipeline'!A:E,4,FALSE)</f>
+        <v>Initial Screening</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>